--- a/麻雀部成績管理.xlsx
+++ b/麻雀部成績管理.xlsx
@@ -2460,7 +2460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:C119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2588,70 +2588,99 @@
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="52" t="inlineStr">
         <is>
-          <t>【ウマ設定の変更】</t>
+          <t>【セッションのアーカイブと復元】</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="53" t="inlineStr">
         <is>
-          <t>「設定」シート D2〜D5 の数値を変更してください（デフォルト: 20/10/-10/-20）</t>
+          <t>・古いセッションを非表示にしたい場合：対象シートをアクティブにして「セッションをアーカイブ」マクロを実行</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="53" t="inlineStr">
         <is>
-          <t>返し点は 設定!C7（デフォルト: 30000）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1"/>
-    <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="52" t="inlineStr">
-        <is>
-          <t>【VBAの追加方法】</t>
-        </is>
-      </c>
-    </row>
+          <t>・アーカイブしたセッションを再表示したい場合：「アーカイブを復元」マクロを実行 → 一覧から番号を選択</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="53" t="inlineStr">
+        <is>
+          <t>※ マスター・設定・データ・使い方・サンプルシートはアーカイブ不可です</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1"/>
     <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="53" t="inlineStr">
-        <is>
-          <t>① Excel で Alt+F11 を押す</t>
+      <c r="B27" s="52" t="inlineStr">
+        <is>
+          <t>【ウマ設定の変更】</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="53" t="inlineStr">
         <is>
-          <t>② 左ペインでブック名を右クリック ▶ 挿入 ▶ 標準モジュール</t>
+          <t>「設定」シート D2〜D5 の数値を変更してください（デフォルト: 20/10/-10/-20）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="53" t="inlineStr">
         <is>
+          <t>返し点は 設定!C7（デフォルト: 30000）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1"/>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="52" t="inlineStr">
+        <is>
+          <t>【VBAの追加方法】</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="53" t="inlineStr">
+        <is>
+          <t>① Excel で Alt+F11 を押す</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="53" t="inlineStr">
+        <is>
+          <t>② 左ペインでブック名を右クリック ▶ 挿入 ▶ 標準モジュール</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="53" t="inlineStr">
+        <is>
           <t>③ 下のコードボックス内のコードを貼り付ける</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="53" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="53" t="inlineStr">
         <is>
           <t>④ Alt+F11 で戻る → [開発] タブ ▶ [マクロ] で実行できます</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1"/>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="54" t="inlineStr">
+    <row r="36" ht="18" customHeight="1"/>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="54" t="inlineStr">
         <is>
           <t>▼ VBAコード（以下をコピーして標準モジュールに貼り付け）</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="55" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="55" t="inlineStr">
         <is>
           <t>' ============================================================
 ' 麻雀部成績管理 - VBAコード（Alt+F11 で貼り付け）
@@ -2660,6 +2689,79 @@
 ' その後 [開発タブ] &gt; [マクロ] から実行できます。
 ' ボタンにマクロを割り当てると便利です。
 ' ============================================================
+' ----------------------------------------------------------
+' セッションシートをアーカイブ（非表示）にする
+' ----------------------------------------------------------
+Sub セッションをアーカイブ()
+    Dim ws As Worksheet: Set ws = ActiveSheet
+    Dim nm As String: nm = ws.Name
+    ' 保護シートはアーカイブ不可
+    Dim forbidden As Variant
+    forbidden = Array("マスター", "データ", "設定", "使い方", _
+                      "第1回(4人用サンプル)", "第1回(8人用サンプル)")
+    Dim f As Variant
+    For Each f In forbidden
+        If nm = f Then
+            MsgBox "「" &amp; nm &amp; "」はアーカイブできません。", vbExclamation
+            Exit Sub
+        End If
+    Next f
+    If MsgBox("「" &amp; nm &amp; "」をアーカイブ（非表示）にしますか？" &amp; Chr(13) &amp; _
+              "「アーカイブを復元」マクロでいつでも再表示できます。", _
+              vbYesNo + vbQuestion, "アーカイブ確認") = vbNo Then Exit Sub
+    ws.Visible = xlSheetHidden
+    MsgBox "「" &amp; nm &amp; "」をアーカイブしました。", vbInformation
+End Sub
+' ----------------------------------------------------------
+' アーカイブされたセッションシートを復元（再表示）する
+' ----------------------------------------------------------
+Sub アーカイブを復元()
+    Dim excluded As Variant
+    excluded = Array("データ", "設定")
+    ' 非表示のセッションシートを収集
+    Dim sheetNames() As String
+    Dim count As Integer: count = 0
+    Dim ws As Worksheet
+    For Each ws In ThisWorkbook.Sheets
+        If ws.Visible = xlSheetHidden Then
+            Dim isExcluded As Boolean: isExcluded = False
+            Dim ex As Variant
+            For Each ex In excluded
+                If ws.Name = ex Then isExcluded = True: Exit For
+            Next ex
+            If Not isExcluded Then
+                count = count + 1
+                ReDim Preserve sheetNames(count - 1)
+                sheetNames(count - 1) = ws.Name
+            End If
+        End If
+    Next ws
+    If count = 0 Then
+        MsgBox "アーカイブされたセッションはありません。", vbInformation
+        Exit Sub
+    End If
+    ' 一覧を表示して番号入力を受け付ける
+    Dim listStr As String: listStr = ""
+    Dim i As Integer
+    For i = 0 To count - 1
+        listStr = listStr &amp; (i + 1) &amp; ". " &amp; sheetNames(i) &amp; Chr(13)
+    Next i
+    Dim input As String
+    input = InputBox("復元するセッションの番号を入力してください:" &amp; Chr(13) &amp; Chr(13) &amp; _
+                     listStr, "アーカイブを復元")
+    If input = "" Then Exit Sub
+    If Not IsNumeric(input) Then
+        MsgBox "番号を入力してください。", vbExclamation: Exit Sub
+    End If
+    Dim idx As Integer: idx = CInt(input)
+    If idx &lt; 1 Or idx &gt; count Then
+        MsgBox "1〜" &amp; count &amp; " の番号を入力してください。", vbExclamation: Exit Sub
+    End If
+    Dim targetName As String: targetName = sheetNames(idx - 1)
+    ThisWorkbook.Sheets(targetName).Visible = xlSheetVisible
+    ThisWorkbook.Sheets(targetName).Activate
+    MsgBox "「" &amp; targetName &amp; "」を復元しました！", vbInformation
+End Sub
 ' ----------------------------------------------------------
 ' 4人用シートを新規作成（テンプレートをコピー）
 ' ----------------------------------------------------------
@@ -2785,11 +2887,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40"/>
     <row r="41"/>
     <row r="42"/>
@@ -2865,11 +2962,16 @@
     <row r="112"/>
     <row r="113"/>
     <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A34:C114"/>
-    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A39:C119"/>
+    <mergeCell ref="A38:C38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/麻雀部成績管理.xlsx
+++ b/麻雀部成績管理.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="+0.0;-0.0;0.0"/>
     <numFmt numFmtId="167" formatCode="+0;-0;0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,11 +108,29 @@
     <font>
       <name val="游ゴシック"/>
       <b val="1"/>
+      <color rgb="007B3F00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
       <color rgb="001B3A6B"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="游ゴシック"/>
+      <color rgb="00222222"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <color rgb="00B71C1C"/>
       <sz val="10"/>
     </font>
     <font>
@@ -121,7 +139,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -200,7 +218,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8F0FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007B1FA2"/>
       </patternFill>
     </fill>
     <fill>
@@ -227,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -364,14 +392,37 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2460,198 +2511,368 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:D159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="44" customHeight="1">
       <c r="A1" s="51" t="inlineStr">
         <is>
-          <t>使い方ガイド</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1"/>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="52" t="inlineStr">
-        <is>
-          <t>【STEP 1】参加者を登録する</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="B4" s="53" t="inlineStr">
-        <is>
-          <t>「設定」シート（非表示）の A列に部員名を追加してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="53" t="inlineStr">
-        <is>
-          <t>→ シートタブを右クリック ▶ [再表示] ▶ 設定 を選択</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1"/>
-    <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="52" t="inlineStr">
-        <is>
-          <t>【STEP 2】各回のシートを作成する</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t>・4人の場合：「新規シート_4人」マクロを実行</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="53" t="inlineStr">
-        <is>
-          <t>・8人の場合：「新規シート_8人」マクロを実行</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="53" t="inlineStr">
-        <is>
-          <t>→ [開発] タブ ▶ [マクロ] ▶ 実行  (または割り当てたボタンを押す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1"/>
-    <row r="12" ht="18" customHeight="1">
-      <c r="B12" s="52" t="inlineStr">
-        <is>
-          <t>【STEP 3】結果を入力する</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="53" t="inlineStr">
-        <is>
-          <t>・参加者：プルダウンから選択</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="53" t="inlineStr">
-        <is>
-          <t>・順位：1〜4 をプルダウンから選択</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="53" t="inlineStr">
-        <is>
-          <t>・点数：素点を入力（例: 42000）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="B16" s="53" t="inlineStr">
-        <is>
-          <t>・ウマ・収支 は自動計算されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="53" t="inlineStr">
-        <is>
-          <t>・8人の場合、A卓とB卓 に分けて入力 → 同卓が一目でわかります</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1"/>
-    <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="52" t="inlineStr">
-        <is>
-          <t>【STEP 4】集計に追加する</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="53" t="inlineStr">
-        <is>
-          <t>「集計に追加」マクロを実行 → 「マスター」シートに自動反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1"/>
-    <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="52" t="inlineStr">
-        <is>
-          <t>【ウマ設定の変更】</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="53" t="inlineStr">
-        <is>
-          <t>「設定」シート D2〜D5 の数値を変更してください（デフォルト: 20/10/-10/-20）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="53" t="inlineStr">
-        <is>
-          <t>返し点は 設定!C7（デフォルト: 30000）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1"/>
-    <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="52" t="inlineStr">
-        <is>
-          <t>【VBAの追加方法】</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="53" t="inlineStr">
-        <is>
-          <t>① Excel で Alt+F11 を押す</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="53" t="inlineStr">
+          <t>使い方ガイド  ―  シーン別操作手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>⚠  このファイルはマクロ（VBA）を使用します。最初に「VBAの設定」セクションを参照してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="53" t="inlineStr">
+        <is>
+          <t>⚙  VBAの設定（はじめに1回だけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="B5" s="54" t="inlineStr">
+        <is>
+          <t>STEP 1 ｜ VBAコードを貼り付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>① Excel で  Alt + F11  を押す（VBAエディターを開く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="C7" s="55" t="inlineStr">
         <is>
           <t>② 左ペインでブック名を右クリック ▶ 挿入 ▶ 標準モジュール</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="53" t="inlineStr">
-        <is>
-          <t>③ 下のコードボックス内のコードを貼り付ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="53" t="inlineStr">
-        <is>
-          <t>④ Alt+F11 で戻る → [開発] タブ ▶ [マクロ] で実行できます</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1"/>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="54" t="inlineStr">
-        <is>
-          <t>▼ VBAコード（以下をコピーして標準モジュールに貼り付け）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="55" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>③ このシート末尾の「VBAコード」を全選択してコピーし、モジュールに貼り付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>④ Alt + F11 で Excel に戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t>STEP 2 ｜ マクロを有効にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>ファイルを開くとき「コンテンツを有効にする」を必ずクリックしてください。</t>
+        </is>
+      </c>
+      <c r="D11" s="56" t="inlineStr">
+        <is>
+          <t>※ .xlsm 形式で保存すること（マクロ有効ブック）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="8" customHeight="1"/>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="57" t="inlineStr">
+        <is>
+          <t>🀇  シーン①  点数を記載したい（基本操作）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="54" t="inlineStr">
+        <is>
+          <t>STEP 1 ｜ 今回の入力シートを作成する</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="C15" s="55" t="inlineStr">
+        <is>
+          <t>・4人で対局 → 「新規シート_4人」マクロを実行</t>
+        </is>
+      </c>
+      <c r="D15" s="56" t="inlineStr">
+        <is>
+          <t>サンプルシートをコピーして日付・回数をセットします</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="C16" s="58" t="inlineStr">
+        <is>
+          <t>▶ マクロ実行: 「新規シート_4人」</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="C17" s="55" t="inlineStr">
+        <is>
+          <t>・8人で対局（A卓／B卓） → 「新規シート_8人」マクロを実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="C18" s="58" t="inlineStr">
+        <is>
+          <t>▶ マクロ実行: 「新規シート_8人」</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="C19" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → 回数・日付を入力するダイアログが出るので入力してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="B20" s="54" t="inlineStr">
+        <is>
+          <t>STEP 2 ｜ 点数を入力する</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="C21" s="55" t="inlineStr">
+        <is>
+          <t>① 参加者列（A列）：プルダウンからメンバー名を選択</t>
+        </is>
+      </c>
+      <c r="D21" s="56" t="inlineStr">
+        <is>
+          <t>名前がない場合は「シーン②メンバー追加」を先に行ってください</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="C22" s="55" t="inlineStr">
+        <is>
+          <t>② 順位列（B列）：1〜4 をプルダウンから選択</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="C23" s="55" t="inlineStr">
+        <is>
+          <t>③ 点数列（C列）：素点を直接入力  （例: 42000）</t>
+        </is>
+      </c>
+      <c r="D23" s="56" t="inlineStr">
+        <is>
+          <t>ウマ・収支は自動計算されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="C24" s="55" t="inlineStr">
+        <is>
+          <t>④ 確認：シート下部の「点数合計」が 100,000 になっていればOK</t>
+        </is>
+      </c>
+      <c r="D24" s="56" t="inlineStr">
+        <is>
+          <t>※ 30,000 × 4人 = 120,000 ではなく持ち点次第で変わります</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="B25" s="54" t="inlineStr">
+        <is>
+          <t>STEP 3 ｜ マスターに反映する</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="C26" s="55" t="inlineStr">
+        <is>
+          <t>入力完了後、「集計に追加」マクロを実行してください。</t>
+        </is>
+      </c>
+      <c r="D26" s="56" t="inlineStr">
+        <is>
+          <t>マスターシートの成績・順位が自動更新されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="C27" s="58" t="inlineStr">
+        <is>
+          <t>▶ マクロ実行: 「集計に追加」</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="C28" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → 同じ回を再登録する場合、上書き確認ダイアログが表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="59" t="inlineStr">
+        <is>
+          <t>👤  シーン②  メンバーを追加したい（特例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="B31" s="54" t="inlineStr">
+        <is>
+          <t>方法A（推奨）｜ マクロで追加する  ※ 最も簡単</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="C32" s="55" t="inlineStr">
+        <is>
+          <t>「メンバー追加」マクロを実行し、名前を入力するだけ。</t>
+        </is>
+      </c>
+      <c r="D32" s="56" t="inlineStr">
+        <is>
+          <t>重複チェックもマクロが行います</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="C33" s="58" t="inlineStr">
+        <is>
+          <t>▶ マクロ実行: 「メンバー追加」</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="C34" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → 次回から点数入力シートのプルダウンに表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="B35" s="54" t="inlineStr">
+        <is>
+          <t>方法B（手動）｜ 設定シートを直接編集する</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="C36" s="55" t="inlineStr">
+        <is>
+          <t>① シートタブを右クリック ▶ [再表示] ▶「設定」を選択</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="C37" s="55" t="inlineStr">
+        <is>
+          <t>② 設定シートの A列（A2 以降）に名前を追記する</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="C38" s="55" t="inlineStr">
+        <is>
+          <t>③ 設定シートを再び非表示にする（任意）</t>
+        </is>
+      </c>
+      <c r="D38" s="56" t="inlineStr">
+        <is>
+          <t>右クリック ▶ [非表示]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="B39" s="54" t="inlineStr">
+        <is>
+          <t>注意事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="C40" s="60" t="inlineStr">
+        <is>
+          <t>・メンバーを削除しても、既存の集計データは残ります（削除は手動でデータシートを編集）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="C41" s="60" t="inlineStr">
+        <is>
+          <t>・名前を変更した場合、過去データの名前は自動で変わりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="8" customHeight="1"/>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="53" t="inlineStr">
+        <is>
+          <t>🔧  その他の設定変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="B44" s="54" t="inlineStr">
+        <is>
+          <t>ウマ・返し点を変更したい</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="C45" s="55" t="inlineStr">
+        <is>
+          <t>設定シート D2〜D5：ウマの値（デフォルト +20 / +10 / -10 / -20）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="C46" s="55" t="inlineStr">
+        <is>
+          <t>設定シート C7：返し点（デフォルト 30000）</t>
+        </is>
+      </c>
+      <c r="D46" s="56" t="inlineStr">
+        <is>
+          <t>変更後は既存シートのウマ・収支も再計算されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="61" t="inlineStr">
+        <is>
+          <t>▼ VBAコード（以下を全選択 → コピーして標準モジュールに貼り付け）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="62" t="inlineStr">
         <is>
           <t>' ============================================================
 ' 麻雀部成績管理 - VBAコード（Alt+F11 で貼り付け）
@@ -2661,7 +2882,31 @@
 ' ボタンにマクロを割り当てると便利です。
 ' ============================================================
 ' ----------------------------------------------------------
-' 4人用シートを新規作成（テンプレートをコピー）
+' 【シーン: メンバーを追加したい】
+' 参加者を「設定」シートのリストに追加する
+' ----------------------------------------------------------
+Sub メンバー追加()
+    Dim newName As String
+    newName = InputBox("追加するメンバーの名前を入力してください。", "メンバー追加")
+    If newName = "" Then Exit Sub
+    Dim wsConfig As Worksheet: Set wsConfig = Sheets("設定")
+    ' 重複チェック
+    Dim lastRow As Long
+    lastRow = wsConfig.Cells(wsConfig.Rows.Count, "A").End(xlUp).Row
+    Dim i As Long
+    For i = 2 To lastRow
+        If wsConfig.Cells(i, 1).Value = newName Then
+            MsgBox "「" &amp; newName &amp; "」は既に登録されています。", vbExclamation
+            Exit Sub
+        End If
+    Next i
+    ' 末尾に追加
+    wsConfig.Cells(lastRow + 1, 1).Value = newName
+    MsgBox "「" &amp; newName &amp; "」を追加しました！" &amp; vbCrLf &amp; _
+           "次回から入力シートのプルダウンに表示されます。", vbInformation
+End Sub
+' ----------------------------------------------------------
+' 【シーン: 点数を記載したい】4人用シートを新規作成
 ' ----------------------------------------------------------
 Sub 新規シート_4人()
     Dim num As String
@@ -2685,7 +2930,7 @@
     MsgBox "「" &amp; newName &amp; "」を作成しました！", vbInformation
 End Sub
 ' ----------------------------------------------------------
-' 8人用シートを新規作成
+' 【シーン: 点数を記載したい】8人用シートを新規作成
 ' ----------------------------------------------------------
 Sub 新規シート_8人()
     Dim num As String
@@ -2710,7 +2955,7 @@
     MsgBox "「" &amp; newName &amp; "」を作成しました！", vbInformation
 End Sub
 ' ----------------------------------------------------------
-' アクティブシートのデータをデータシートに集計
+' 【シーン: 点数を記載したい】アクティブシートのデータを集計
 ' ----------------------------------------------------------
 Sub 集計に追加()
     Dim ws     As Worksheet: Set ws = ActiveSheet
@@ -2735,7 +2980,7 @@
     End If
     Dim lastRow As Long
     Dim r As Integer
-    ' ── 4人シート判定（B2行から下に4行 or 8行）
+    ' ── 4人シート判定（8人 or 4人）
     Dim is8player As Boolean
     is8player = (InStr(ws.Name, "8人") &gt; 0 Or ws.Range("A13").Value &lt;&gt; "")
     If is8player Then
@@ -2785,21 +3030,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
     <row r="50"/>
     <row r="51"/>
     <row r="52"/>
@@ -2865,11 +3095,74 @@
     <row r="112"/>
     <row r="113"/>
     <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A34:C114"/>
-    <mergeCell ref="A33:C33"/>
+  <mergeCells count="21">
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A49:D159"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B39:D39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
